--- a/02_DIA_inicio_2026_analisis_assets/rbd_9426_escuela-llano-subercaseaux_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9426_escuela-llano-subercaseaux_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F69952D7-7DB3-43F0-9963-8CFF7A947222}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09B4A3A3-25F2-40C7-AE1A-281D7E15FEC9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5361219-EDB6-4280-ABB6-B2DC60921585}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67EEB577-7052-42B3-BB87-BDA8DBBB8076}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9809C6-13CB-44C3-BCFE-1D0BAAAB41A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A9CFEC-832A-46DA-9BC6-F6601A08D723}"/>
 </file>